--- a/Proyecto Interno/review-food-security-paper/07_tables/final/tab01_cost_annual.xlsx
+++ b/Proyecto Interno/review-food-security-paper/07_tables/final/tab01_cost_annual.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="210">
   <si>
     <t xml:space="preserve">Table 1A. Mean nominal per capita daily diet costs (COP/day)</t>
   </si>
@@ -43,7 +43,7 @@
     <t xml:space="preserve">2,083 (380)</t>
   </si>
   <si>
-    <t xml:space="preserve">4,020 (909)</t>
+    <t xml:space="preserve">4,080 (944)</t>
   </si>
   <si>
     <t xml:space="preserve">6,135 (1,449)</t>
@@ -55,7 +55,7 @@
     <t xml:space="preserve">1,717 (16)</t>
   </si>
   <si>
-    <t xml:space="preserve">2,961 (57)</t>
+    <t xml:space="preserve">2,977 (59)</t>
   </si>
   <si>
     <t xml:space="preserve">4,436 (116)</t>
@@ -67,7 +67,7 @@
     <t xml:space="preserve">1,760 (18)</t>
   </si>
   <si>
-    <t xml:space="preserve">3,181 (55)</t>
+    <t xml:space="preserve">3,209 (56)</t>
   </si>
   <si>
     <t xml:space="preserve">4,866 (100)</t>
@@ -79,7 +79,7 @@
     <t xml:space="preserve">1,810 (80)</t>
   </si>
   <si>
-    <t xml:space="preserve">3,404 (122)</t>
+    <t xml:space="preserve">3,442 (127)</t>
   </si>
   <si>
     <t xml:space="preserve">5,125 (191)</t>
@@ -91,7 +91,7 @@
     <t xml:space="preserve">2,295 (237)</t>
   </si>
   <si>
-    <t xml:space="preserve">4,324 (365)</t>
+    <t xml:space="preserve">4,395 (376)</t>
   </si>
   <si>
     <t xml:space="preserve">6,548 (564)</t>
@@ -103,7 +103,7 @@
     <t xml:space="preserve">2,707 (174)</t>
   </si>
   <si>
-    <t xml:space="preserve">5,116 (69)</t>
+    <t xml:space="preserve">5,235 (74)</t>
   </si>
   <si>
     <t xml:space="preserve">7,846 (136)</t>
@@ -115,7 +115,7 @@
     <t xml:space="preserve">2,207 (86)</t>
   </si>
   <si>
-    <t xml:space="preserve">5,136 (42)</t>
+    <t xml:space="preserve">5,222 (41)</t>
   </si>
   <si>
     <t xml:space="preserve">7,989 (120)</t>
@@ -127,7 +127,7 @@
     <t xml:space="preserve">2,027 (364)</t>
   </si>
   <si>
-    <t xml:space="preserve">4,189 (919)</t>
+    <t xml:space="preserve">4,233 (946)</t>
   </si>
   <si>
     <t xml:space="preserve">5,948 (1,341)</t>
@@ -136,7 +136,7 @@
     <t xml:space="preserve">1,672 (23)</t>
   </si>
   <si>
-    <t xml:space="preserve">3,087 (70)</t>
+    <t xml:space="preserve">3,101 (69)</t>
   </si>
   <si>
     <t xml:space="preserve">4,333 (78)</t>
@@ -145,25 +145,25 @@
     <t xml:space="preserve">1,689 (17)</t>
   </si>
   <si>
-    <t xml:space="preserve">3,335 (72)</t>
+    <t xml:space="preserve">3,354 (73)</t>
   </si>
   <si>
     <t xml:space="preserve">4,724 (110)</t>
   </si>
   <si>
-    <t xml:space="preserve">1,774 (62)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,574 (155)</t>
+    <t xml:space="preserve">1,774 (63)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,603 (159)</t>
   </si>
   <si>
     <t xml:space="preserve">5,039 (229)</t>
   </si>
   <si>
-    <t xml:space="preserve">2,201 (203)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,577 (352)</t>
+    <t xml:space="preserve">2,201 (202)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,627 (361)</t>
   </si>
   <si>
     <t xml:space="preserve">6,527 (534)</t>
@@ -172,7 +172,7 @@
     <t xml:space="preserve">2,628 (113)</t>
   </si>
   <si>
-    <t xml:space="preserve">5,278 (55)</t>
+    <t xml:space="preserve">5,365 (56)</t>
   </si>
   <si>
     <t xml:space="preserve">7,496 (157)</t>
@@ -181,7 +181,7 @@
     <t xml:space="preserve">2,200 (81)</t>
   </si>
   <si>
-    <t xml:space="preserve">5,281 (55)</t>
+    <t xml:space="preserve">5,349 (56)</t>
   </si>
   <si>
     <t xml:space="preserve">7,567 (115)</t>
@@ -193,7 +193,7 @@
     <t xml:space="preserve">2,013 (353)</t>
   </si>
   <si>
-    <t xml:space="preserve">4,195 (982)</t>
+    <t xml:space="preserve">4,221 (1,013)</t>
   </si>
   <si>
     <t xml:space="preserve">6,018 (1,435)</t>
@@ -202,7 +202,7 @@
     <t xml:space="preserve">1,646 (20)</t>
   </si>
   <si>
-    <t xml:space="preserve">3,029 (68)</t>
+    <t xml:space="preserve">3,018 (65)</t>
   </si>
   <si>
     <t xml:space="preserve">4,317 (81)</t>
@@ -211,7 +211,7 @@
     <t xml:space="preserve">1,708 (24)</t>
   </si>
   <si>
-    <t xml:space="preserve">3,286 (56)</t>
+    <t xml:space="preserve">3,284 (60)</t>
   </si>
   <si>
     <t xml:space="preserve">4,727 (91)</t>
@@ -220,7 +220,7 @@
     <t xml:space="preserve">1,805 (61)</t>
   </si>
   <si>
-    <t xml:space="preserve">3,548 (157)</t>
+    <t xml:space="preserve">3,551 (159)</t>
   </si>
   <si>
     <t xml:space="preserve">5,053 (189)</t>
@@ -229,7 +229,7 @@
     <t xml:space="preserve">2,230 (207)</t>
   </si>
   <si>
-    <t xml:space="preserve">4,547 (362)</t>
+    <t xml:space="preserve">4,583 (362)</t>
   </si>
   <si>
     <t xml:space="preserve">6,478 (529)</t>
@@ -238,7 +238,7 @@
     <t xml:space="preserve">2,595 (148)</t>
   </si>
   <si>
-    <t xml:space="preserve">5,431 (109)</t>
+    <t xml:space="preserve">5,495 (118)</t>
   </si>
   <si>
     <t xml:space="preserve">7,736 (230)</t>
@@ -247,7 +247,7 @@
     <t xml:space="preserve">2,092 (101)</t>
   </si>
   <si>
-    <t xml:space="preserve">5,327 (81)</t>
+    <t xml:space="preserve">5,394 (99)</t>
   </si>
   <si>
     <t xml:space="preserve">7,797 (114)</t>
@@ -262,7 +262,7 @@
     <t xml:space="preserve">1,507 (146)</t>
   </si>
   <si>
-    <t xml:space="preserve">2,867 (60)</t>
+    <t xml:space="preserve">2,906 (73)</t>
   </si>
   <si>
     <t xml:space="preserve">4,366 (129)</t>
@@ -271,7 +271,7 @@
     <t xml:space="preserve">1,640 (18)</t>
   </si>
   <si>
-    <t xml:space="preserve">2,827 (24)</t>
+    <t xml:space="preserve">2,843 (27)</t>
   </si>
   <si>
     <t xml:space="preserve">4,236 (57)</t>
@@ -280,7 +280,7 @@
     <t xml:space="preserve">1,598 (21)</t>
   </si>
   <si>
-    <t xml:space="preserve">2,889 (11)</t>
+    <t xml:space="preserve">2,914 (12)</t>
   </si>
   <si>
     <t xml:space="preserve">4,418 (24)</t>
@@ -289,7 +289,7 @@
     <t xml:space="preserve">1,495 (27)</t>
   </si>
   <si>
-    <t xml:space="preserve">2,813 (41)</t>
+    <t xml:space="preserve">2,843 (39)</t>
   </si>
   <si>
     <t xml:space="preserve">4,234 (58)</t>
@@ -298,7 +298,7 @@
     <t xml:space="preserve">1,514 (77)</t>
   </si>
   <si>
-    <t xml:space="preserve">2,855 (78)</t>
+    <t xml:space="preserve">2,901 (82)</t>
   </si>
   <si>
     <t xml:space="preserve">4,323 (126)</t>
@@ -307,7 +307,7 @@
     <t xml:space="preserve">1,561 (110)</t>
   </si>
   <si>
-    <t xml:space="preserve">2,949 (29)</t>
+    <t xml:space="preserve">3,017 (34)</t>
   </si>
   <si>
     <t xml:space="preserve">4,522 (72)</t>
@@ -316,7 +316,7 @@
     <t xml:space="preserve">1,234 (61)</t>
   </si>
   <si>
-    <t xml:space="preserve">2,869 (36)</t>
+    <t xml:space="preserve">2,917 (41)</t>
   </si>
   <si>
     <t xml:space="preserve">4,462 (18)</t>
@@ -325,7 +325,7 @@
     <t xml:space="preserve">1,460 (123)</t>
   </si>
   <si>
-    <t xml:space="preserve">2,980 (48)</t>
+    <t xml:space="preserve">3,009 (55)</t>
   </si>
   <si>
     <t xml:space="preserve">4,226 (93)</t>
@@ -334,7 +334,7 @@
     <t xml:space="preserve">1,602 (31)</t>
   </si>
   <si>
-    <t xml:space="preserve">2,958 (17)</t>
+    <t xml:space="preserve">2,971 (17)</t>
   </si>
   <si>
     <t xml:space="preserve">4,151 (22)</t>
@@ -343,7 +343,7 @@
     <t xml:space="preserve">1,518 (17)</t>
   </si>
   <si>
-    <t xml:space="preserve">2,996 (29)</t>
+    <t xml:space="preserve">3,014 (29)</t>
   </si>
   <si>
     <t xml:space="preserve">4,244 (54)</t>
@@ -352,7 +352,7 @@
     <t xml:space="preserve">1,454 (22)</t>
   </si>
   <si>
-    <t xml:space="preserve">2,928 (25)</t>
+    <t xml:space="preserve">2,951 (24)</t>
   </si>
   <si>
     <t xml:space="preserve">4,127 (37)</t>
@@ -361,7 +361,7 @@
     <t xml:space="preserve">1,444 (47)</t>
   </si>
   <si>
-    <t xml:space="preserve">3,005 (50)</t>
+    <t xml:space="preserve">3,038 (53)</t>
   </si>
   <si>
     <t xml:space="preserve">4,285 (103)</t>
@@ -370,7 +370,7 @@
     <t xml:space="preserve">1,511 (70)</t>
   </si>
   <si>
-    <t xml:space="preserve">3,035 (30)</t>
+    <t xml:space="preserve">3,085 (30)</t>
   </si>
   <si>
     <t xml:space="preserve">4,310 (102)</t>
@@ -379,7 +379,7 @@
     <t xml:space="preserve">1,232 (53)</t>
   </si>
   <si>
-    <t xml:space="preserve">2,957 (39)</t>
+    <t xml:space="preserve">2,995 (42)</t>
   </si>
   <si>
     <t xml:space="preserve">4,237 (44)</t>
@@ -388,7 +388,7 @@
     <t xml:space="preserve">1,397 (151)</t>
   </si>
   <si>
-    <t xml:space="preserve">2,857 (75)</t>
+    <t xml:space="preserve">2,871 (83)</t>
   </si>
   <si>
     <t xml:space="preserve">4,096 (107)</t>
@@ -397,7 +397,7 @@
     <t xml:space="preserve">1,540 (45)</t>
   </si>
   <si>
-    <t xml:space="preserve">2,831 (31)</t>
+    <t xml:space="preserve">2,821 (32)</t>
   </si>
   <si>
     <t xml:space="preserve">4,036 (40)</t>
@@ -406,7 +406,7 @@
     <t xml:space="preserve">1,497 (20)</t>
   </si>
   <si>
-    <t xml:space="preserve">2,880 (52)</t>
+    <t xml:space="preserve">2,878 (50)</t>
   </si>
   <si>
     <t xml:space="preserve">4,142 (37)</t>
@@ -415,7 +415,7 @@
     <t xml:space="preserve">1,429 (58)</t>
   </si>
   <si>
-    <t xml:space="preserve">2,806 (74)</t>
+    <t xml:space="preserve">2,809 (75)</t>
   </si>
   <si>
     <t xml:space="preserve">3,997 (91)</t>
@@ -424,7 +424,7 @@
     <t xml:space="preserve">1,401 (57)</t>
   </si>
   <si>
-    <t xml:space="preserve">2,857 (64)</t>
+    <t xml:space="preserve">2,879 (60)</t>
   </si>
   <si>
     <t xml:space="preserve">4,070 (107)</t>
@@ -433,7 +433,7 @@
     <t xml:space="preserve">1,413 (87)</t>
   </si>
   <si>
-    <t xml:space="preserve">2,956 (40)</t>
+    <t xml:space="preserve">2,991 (48)</t>
   </si>
   <si>
     <t xml:space="preserve">4,211 (126)</t>
@@ -442,7 +442,7 @@
     <t xml:space="preserve">1,106 (65)</t>
   </si>
   <si>
-    <t xml:space="preserve">2,816 (72)</t>
+    <t xml:space="preserve">2,851 (76)</t>
   </si>
   <si>
     <t xml:space="preserve">4,120 (40)</t>
@@ -460,193 +460,190 @@
     <t xml:space="preserve">CoRD/CoNA</t>
   </si>
   <si>
-    <t xml:space="preserve">1.921 (0.205)</t>
+    <t xml:space="preserve">1.948 (0.213)</t>
   </si>
   <si>
     <t xml:space="preserve">2.929 (0.349)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.523 (0.023)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.724 (0.020)</t>
+    <t xml:space="preserve">1.502 (0.020)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.734 (0.021)</t>
   </si>
   <si>
     <t xml:space="preserve">2.583 (0.047)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.498 (0.012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.808 (0.027)</t>
+    <t xml:space="preserve">1.490 (0.011)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.823 (0.028)</t>
   </si>
   <si>
     <t xml:space="preserve">2.765 (0.045)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.530 (0.011)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.882 (0.025)</t>
+    <t xml:space="preserve">1.516 (0.011)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.902 (0.023)</t>
   </si>
   <si>
     <t xml:space="preserve">2.833 (0.034)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.506 (0.008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.888 (0.069)</t>
+    <t xml:space="preserve">1.489 (0.007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.919 (0.070)</t>
   </si>
   <si>
     <t xml:space="preserve">2.859 (0.119)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.514 (0.012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.897 (0.124)</t>
+    <t xml:space="preserve">1.941 (0.126)</t>
   </si>
   <si>
     <t xml:space="preserve">2.908 (0.179)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.533 (0.011)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.329 (0.083)</t>
+    <t xml:space="preserve">1.499 (0.009)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.368 (0.081)</t>
   </si>
   <si>
     <t xml:space="preserve">3.625 (0.176)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.556 (0.021)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.055 (0.180)</t>
+    <t xml:space="preserve">1.530 (0.023)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.076 (0.186)</t>
   </si>
   <si>
     <t xml:space="preserve">2.916 (0.276)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.418 (0.020)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.847 (0.045)</t>
+    <t xml:space="preserve">1.404 (0.018)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.855 (0.044)</t>
   </si>
   <si>
     <t xml:space="preserve">2.592 (0.048)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.404 (0.012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.974 (0.039)</t>
+    <t xml:space="preserve">1.397 (0.012)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.986 (0.039)</t>
   </si>
   <si>
     <t xml:space="preserve">2.797 (0.043)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.417 (0.022)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.014 (0.022)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.840 (0.038)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.410 (0.005)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.083 (0.058)</t>
+    <t xml:space="preserve">1.408 (0.022)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.030 (0.022)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.839 (0.037)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.398 (0.005)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.105 (0.057)</t>
   </si>
   <si>
     <t xml:space="preserve">2.969 (0.098)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.426 (0.013)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.012 (0.076)</t>
+    <t xml:space="preserve">1.410 (0.012)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.045 (0.078)</t>
   </si>
   <si>
     <t xml:space="preserve">2.855 (0.074)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.420 (0.021)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.403 (0.073)</t>
+    <t xml:space="preserve">1.397 (0.020)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.434 (0.071)</t>
   </si>
   <si>
     <t xml:space="preserve">3.444 (0.153)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.433 (0.025)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.070 (0.243)</t>
+    <t xml:space="preserve">1.415 (0.026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.081 (0.255)</t>
   </si>
   <si>
     <t xml:space="preserve">2.970 (0.381)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.434 (0.028)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.840 (0.048)</t>
+    <t xml:space="preserve">1.427 (0.026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.833 (0.046)</t>
   </si>
   <si>
     <t xml:space="preserve">2.623 (0.058)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.426 (0.010)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.924 (0.036)</t>
+    <t xml:space="preserve">1.431 (0.010)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.923 (0.032)</t>
   </si>
   <si>
     <t xml:space="preserve">2.767 (0.034)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.439 (0.023)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.965 (0.036)</t>
+    <t xml:space="preserve">1.439 (0.020)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.967 (0.036)</t>
   </si>
   <si>
     <t xml:space="preserve">2.800 (0.065)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.425 (0.023)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.042 (0.077)</t>
+    <t xml:space="preserve">1.423 (0.024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.058 (0.078)</t>
   </si>
   <si>
     <t xml:space="preserve">2.910 (0.146)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.425 (0.024)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.100 (0.132)</t>
+    <t xml:space="preserve">1.413 (0.021)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.124 (0.128)</t>
   </si>
   <si>
     <t xml:space="preserve">2.988 (0.151)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.425 (0.031)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.550 (0.085)</t>
+    <t xml:space="preserve">1.408 (0.026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.582 (0.085)</t>
   </si>
   <si>
     <t xml:space="preserve">3.735 (0.185)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.464 (0.031)</t>
+    <t xml:space="preserve">1.446 (0.030)</t>
   </si>
 </sst>
 </file>
@@ -1971,7 +1968,7 @@
         <v>161</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8">
@@ -1982,13 +1979,13 @@
         <v>27</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="9">
@@ -1999,13 +1996,13 @@
         <v>31</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="10">
@@ -2016,13 +2013,13 @@
         <v>7</v>
       </c>
       <c r="C10" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="E10" s="6" t="s">
         <v>170</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="11">
@@ -2033,13 +2030,13 @@
         <v>11</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="E11" s="5" t="s">
         <v>173</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="12">
@@ -2050,13 +2047,13 @@
         <v>15</v>
       </c>
       <c r="C12" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="E12" s="5" t="s">
         <v>176</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="13">
@@ -2067,13 +2064,13 @@
         <v>19</v>
       </c>
       <c r="C13" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="5" t="s">
         <v>179</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="14">
@@ -2084,13 +2081,13 @@
         <v>23</v>
       </c>
       <c r="C14" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="5" t="s">
         <v>182</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="15">
@@ -2101,13 +2098,13 @@
         <v>27</v>
       </c>
       <c r="C15" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="E15" s="5" t="s">
         <v>185</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="16">
@@ -2118,13 +2115,13 @@
         <v>31</v>
       </c>
       <c r="C16" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="5" t="s">
         <v>188</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="17">
@@ -2135,13 +2132,13 @@
         <v>7</v>
       </c>
       <c r="C17" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="E17" s="4" t="s">
         <v>191</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="18">
@@ -2152,13 +2149,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>194</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="19">
@@ -2169,13 +2166,13 @@
         <v>15</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="3" t="s">
         <v>197</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="20">
@@ -2186,13 +2183,13 @@
         <v>19</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>200</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="21">
@@ -2203,13 +2200,13 @@
         <v>23</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="22">
@@ -2220,13 +2217,13 @@
         <v>27</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>206</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="23">
@@ -2237,13 +2234,13 @@
         <v>31</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="24" ht="35" customHeight="1">
